--- a/indice_matrices.xlsx
+++ b/indice_matrices.xlsx
@@ -14,20 +14,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="49">
   <si>
     <t>pais</t>
   </si>
   <si>
+    <t>serie_fuente</t>
+  </si>
+  <si>
     <t>anio</t>
   </si>
   <si>
     <t>archivo</t>
   </si>
   <si>
-    <t>fuente_excel</t>
-  </si>
-  <si>
     <t>Argentina</t>
   </si>
   <si>
@@ -40,106 +40,25 @@
     <t>Uruguay</t>
   </si>
   <si>
-    <t>MIP\Argentina\MIP_Argentina_1997.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Argentina\MIP_Argentina_2004.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Argentina\MIP_Argentina_2018.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Argentina\MIP_Argentina_2019.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Argentina\MIP_Argentina_2020.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Argentina\MIP_Argentina_2021.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2000.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2001.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2002.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2003.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2004.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2005.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2006.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2007.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2008.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2009.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2010.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2011.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2012.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2013.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2014.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2015.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2016.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2017.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2018.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2019.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2020.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Brasil\MIP_Brasil_2021.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Mexico\MIP_Mexico_2003.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Mexico\MIP_Mexico_2008.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Mexico\MIP_Mexico_2013.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Mexico\MIP_Mexico_2018.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Uruguay\MIP_Uruguay_2016.xlsx</t>
-  </si>
-  <si>
-    <t>MIP\Uruguay\MIP_Uruguay_2017.xlsx</t>
+    <t>argentina_mip97</t>
+  </si>
+  <si>
+    <t>argentina</t>
+  </si>
+  <si>
+    <t>brasil_early</t>
+  </si>
+  <si>
+    <t>brasil</t>
+  </si>
+  <si>
+    <t>mexico</t>
+  </si>
+  <si>
+    <t>uruguay</t>
+  </si>
+  <si>
+    <t>uruguay_cou</t>
   </si>
   <si>
     <t>output\matrices_insumo_producto\Argentina\MIP_Argentina_1997.xlsx</t>
@@ -620,476 +539,476 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
         <v>1997</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
         <v>2004</v>
       </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
         <v>2018</v>
       </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
         <v>2019</v>
       </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
         <v>2020</v>
       </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
         <v>2021</v>
       </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
         <v>2000</v>
       </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>5</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
         <v>2001</v>
       </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10">
         <v>2002</v>
       </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11">
         <v>2003</v>
       </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>5</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
         <v>2004</v>
       </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>5</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
         <v>2005</v>
       </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>5</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14">
         <v>2006</v>
       </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>5</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15">
         <v>2007</v>
       </c>
-      <c r="C15" t="s">
-        <v>21</v>
-      </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>5</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16">
         <v>2008</v>
       </c>
-      <c r="C16" t="s">
-        <v>22</v>
-      </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>5</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17">
         <v>2009</v>
       </c>
-      <c r="C17" t="s">
-        <v>23</v>
-      </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>5</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18">
         <v>2010</v>
       </c>
-      <c r="C18" t="s">
-        <v>24</v>
-      </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>5</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19">
         <v>2011</v>
       </c>
-      <c r="C19" t="s">
-        <v>25</v>
-      </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>5</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20">
         <v>2012</v>
       </c>
-      <c r="C20" t="s">
-        <v>26</v>
-      </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>5</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21">
         <v>2013</v>
       </c>
-      <c r="C21" t="s">
-        <v>27</v>
-      </c>
       <c r="D21" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>5</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22">
         <v>2014</v>
       </c>
-      <c r="C22" t="s">
-        <v>28</v>
-      </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>5</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23">
         <v>2015</v>
       </c>
-      <c r="C23" t="s">
-        <v>29</v>
-      </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>5</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24">
         <v>2016</v>
       </c>
-      <c r="C24" t="s">
-        <v>30</v>
-      </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>5</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25">
         <v>2017</v>
       </c>
-      <c r="C25" t="s">
-        <v>31</v>
-      </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>5</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26">
         <v>2018</v>
       </c>
-      <c r="C26" t="s">
-        <v>32</v>
-      </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>5</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27">
         <v>2019</v>
       </c>
-      <c r="C27" t="s">
-        <v>33</v>
-      </c>
       <c r="D27" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>5</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28">
         <v>2020</v>
       </c>
-      <c r="C28" t="s">
-        <v>34</v>
-      </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>5</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29">
         <v>2021</v>
       </c>
-      <c r="C29" t="s">
-        <v>35</v>
-      </c>
       <c r="D29" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>6</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30">
         <v>2003</v>
       </c>
-      <c r="C30" t="s">
-        <v>36</v>
-      </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>6</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31">
         <v>2008</v>
       </c>
-      <c r="C31" t="s">
-        <v>37</v>
-      </c>
       <c r="D31" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>6</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32">
         <v>2013</v>
       </c>
-      <c r="C32" t="s">
-        <v>38</v>
-      </c>
       <c r="D32" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>6</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33">
         <v>2018</v>
       </c>
-      <c r="C33" t="s">
-        <v>39</v>
-      </c>
       <c r="D33" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
         <v>7</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34">
         <v>2016</v>
       </c>
-      <c r="C34" t="s">
-        <v>40</v>
-      </c>
       <c r="D34" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
         <v>7</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35">
         <v>2017</v>
       </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
       <c r="D35" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/indice_matrices.xlsx
+++ b/indice_matrices.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="52">
   <si>
     <t>pais</t>
   </si>
@@ -55,6 +55,9 @@
     <t>mexico</t>
   </si>
   <si>
+    <t>uruguay_cou_2012</t>
+  </si>
+  <si>
     <t>uruguay</t>
   </si>
   <si>
@@ -158,6 +161,9 @@
   </si>
   <si>
     <t>output\matrices_insumo_producto\Mexico\MIP_Mexico_2018.xlsx</t>
+  </si>
+  <si>
+    <t>output\matrices_insumo_producto\Uruguay\MIP_Uruguay_2012.xlsx</t>
   </si>
   <si>
     <t>output\matrices_insumo_producto\Uruguay\MIP_Uruguay_2016.xlsx</t>
@@ -521,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -549,7 +555,7 @@
         <v>1997</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -563,7 +569,7 @@
         <v>2004</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -577,7 +583,7 @@
         <v>2018</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -591,7 +597,7 @@
         <v>2019</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -605,7 +611,7 @@
         <v>2020</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -619,7 +625,7 @@
         <v>2021</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -633,7 +639,7 @@
         <v>2022</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -647,7 +653,7 @@
         <v>2000</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -661,7 +667,7 @@
         <v>2001</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -675,7 +681,7 @@
         <v>2002</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -689,7 +695,7 @@
         <v>2003</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -703,7 +709,7 @@
         <v>2004</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -717,7 +723,7 @@
         <v>2005</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -731,7 +737,7 @@
         <v>2006</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -745,7 +751,7 @@
         <v>2007</v>
       </c>
       <c r="D16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -759,7 +765,7 @@
         <v>2008</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -773,7 +779,7 @@
         <v>2009</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -787,7 +793,7 @@
         <v>2010</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -801,7 +807,7 @@
         <v>2011</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -815,7 +821,7 @@
         <v>2012</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -829,7 +835,7 @@
         <v>2013</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -843,7 +849,7 @@
         <v>2014</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -857,7 +863,7 @@
         <v>2015</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -871,7 +877,7 @@
         <v>2016</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -885,7 +891,7 @@
         <v>2017</v>
       </c>
       <c r="D26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -899,7 +905,7 @@
         <v>2018</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -913,7 +919,7 @@
         <v>2019</v>
       </c>
       <c r="D28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -927,7 +933,7 @@
         <v>2020</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -941,7 +947,7 @@
         <v>2021</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -955,7 +961,7 @@
         <v>2003</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -969,7 +975,7 @@
         <v>2008</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -983,7 +989,7 @@
         <v>2013</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -997,7 +1003,7 @@
         <v>2018</v>
       </c>
       <c r="D34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1008,10 +1014,10 @@
         <v>13</v>
       </c>
       <c r="C35">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="D35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1022,10 +1028,24 @@
         <v>14</v>
       </c>
       <c r="C36">
+        <v>2016</v>
+      </c>
+      <c r="D36" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37">
         <v>2017</v>
       </c>
-      <c r="D36" t="s">
-        <v>49</v>
+      <c r="D37" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
